--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo da Sprint" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="251">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">OBSERVAÇÃO DE CONTROLE</t>
   </si>
   <si>
-    <t xml:space="preserve">A Sprint 3 ainda está sem quantidade entregue na aba “Evolução do Projeto”; por isso aparece como “Atualizar” e não foi inventado nenhum valor.</t>
+    <t xml:space="preserve">A aprovação dos Fluxos() deverão ocorrer na próxima sprint</t>
   </si>
   <si>
     <t xml:space="preserve">HISTÓRICO DE FUNCIONALIDADES ENTREGUES</t>
@@ -454,6 +454,54 @@
     <t xml:space="preserve">PLANEJAMENTO DA PRÓXIMA SPRINT</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprint 5 - 21.09.2026 a 02.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento de requisitos Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A fazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Indexadores, Ready Indexadores, Update Indexadores, Delete Indexadores) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste automatizado funcionalidade de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento de requisitos Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Segmentação, Ready Segmentação, Update Segmentação, Delete Segmentação) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste automatizado funcionalidade de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade Configurações Gerais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade Configurações Gerais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Configurações Gerais, Ready Configurações Gerais, Update Configurações Gerais, Delete Configurações Gerais) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PENDÊNCIAS, DÚVIDAS E DECISÕES</t>
   </si>
   <si>
@@ -524,9 +572,6 @@
   </si>
   <si>
     <t xml:space="preserve">Entregas acumuladas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 5 - 21.09.2026 a 02.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint 6 - 05.10.2026 a 16.10.2026</t>
@@ -809,24 +854,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -839,23 +880,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1105,42 +1129,42 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="D6" s="3" t="n">
+      <c r="B6" s="2"/>
+      <c r="D6" s="2" t="n">
         <f aca="false">SUM(B12:B15)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="G6" s="3" t="n">
+      <c r="E6" s="2"/>
+      <c r="G6" s="2" t="n">
         <f aca="false">SUM(C12:C15)</f>
         <v>41</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="n">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="n">
         <f aca="false">IFERROR(SUM(C12:C15)/SUM(B12:B15),0)</f>
         <v>1</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="e">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="e">
         <f aca="false">#ERR520!</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="4" t="e">
+      <c r="E9" s="3" t="e">
         <f aca="false">#ERR520!</f>
         <v>#N/A</v>
       </c>
@@ -1156,157 +1180,157 @@
       <c r="F10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="str">
+      <c r="A12" s="3" t="str">
         <f aca="false">'Evolução do Projeto'!A5</f>
         <v>Sprint 0 - 13.07.2026 a 24.07.2026</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <f aca="false">'Evolução do Projeto'!B5</f>
         <v>3</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <f aca="false">'Evolução do Projeto'!C5</f>
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <f aca="false">IF(C12="", "", IFERROR(C12/B12,0))</f>
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="str">
+      <c r="E12" s="3" t="str">
         <f aca="false">IF(C12="","Atualizar",IF(C12&gt;=B12,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F12" s="4" t="str">
+      <c r="F12" s="3" t="str">
         <f aca="false">IFERROR(MID(A12,FIND("-",A12)+2,99),"")</f>
         <v>13.07.2026 a 24.07.2026</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="str">
+      <c r="A13" s="3" t="str">
         <f aca="false">'Evolução do Projeto'!A6</f>
         <v>Sprint 1 - 27.07.2026 a 07.08.2026</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <f aca="false">IF(C13="", "", IFERROR(C13/B13,0))</f>
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="str">
+      <c r="E13" s="3" t="str">
         <f aca="false">IF(C13="","Atualizar",IF(C13&gt;=B13,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F13" s="4" t="str">
+      <c r="F13" s="3" t="str">
         <f aca="false">IFERROR(MID(A13,FIND("-",A13)+2,99),"")</f>
         <v>27.07.2026 a 07.08.2026</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="str">
+      <c r="A14" s="3" t="str">
         <f aca="false">'Evolução do Projeto'!A7</f>
         <v>Sprint 2 - 10.08.2026 a 21.08.2026</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <f aca="false">IF(C14="", "", IFERROR(C14/B14,0))</f>
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="str">
+      <c r="E14" s="3" t="str">
         <f aca="false">IF(C14="","Atualizar",IF(C14&gt;=B14,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F14" s="4" t="str">
+      <c r="F14" s="3" t="str">
         <f aca="false">IFERROR(MID(A14,FIND("-",A14)+2,99),"")</f>
         <v>10.08.2026 a 21.08.2026</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="str">
+      <c r="A15" s="3" t="str">
         <f aca="false">'Evolução do Projeto'!A8</f>
         <v>Sprint 3 - 24.08.2026 a 04.09.2026</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="3" t="n">
         <f aca="false">'Evolução do Projeto'!B8</f>
         <v>12</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <f aca="false">IF(C15="", "", IFERROR(C15/B15,0))</f>
         <v>1</v>
       </c>
-      <c r="E15" s="4" t="str">
+      <c r="E15" s="3" t="str">
         <f aca="false">IF(C15="","Atualizar",IF(C15&gt;=B15,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F15" s="4" t="str">
+      <c r="F15" s="3" t="str">
         <f aca="false">IFERROR(MID(A15,FIND("-",A15)+2,99),"")</f>
         <v>24.08.2026 a 04.09.2026</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="3" t="str">
         <f aca="false">'Evolução do Projeto'!A9</f>
         <v>Sprint 4 - 08.09.2026 a 18.09.2026</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="3" t="n">
         <f aca="false">'Evolução do Projeto'!B9</f>
         <v>10</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <f aca="false">IF(C16="", "", IFERROR(C16/B16,0))</f>
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="str">
+      <c r="E16" s="3" t="str">
         <f aca="false">IF(C16="","Atualizar",IF(C16&gt;=B16,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F16" s="4" t="str">
+      <c r="F16" s="3" t="str">
         <f aca="false">IFERROR(MID(A16,FIND("-",A16)+2,99),"")</f>
         <v>08.09.2026 a 18.09.2026</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1342,6 +1366,11 @@
   </sheetPr>
   <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="40.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="42.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="37.34"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1369,1103 +1398,1103 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="3" t="n">
         <f aca="false">COUNTA(B5:B500)</f>
         <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="3" t="n">
         <f aca="false">COUNTIF(F5:F500,"Entregue")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="3" t="n">
         <v>1947</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="n">
         <v>1948</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="3" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 1")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="n">
         <v>1961</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="3" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 2")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="3" t="n">
         <v>1962</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="3" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 3")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="3" t="n">
         <v>1963</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="3" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 4")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="3" t="n">
         <v>1973</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <v>1974</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="3" t="n">
         <v>1975</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="3" t="n">
         <v>1967</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="3" t="n">
         <v>1968</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="3" t="n">
         <v>1969</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="E19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="4" t="s">
+      <c r="E20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="E22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="E23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="E24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="4" t="s">
+      <c r="E25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="E26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="E27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="E28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="4" t="s">
+      <c r="E29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="E31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="4" t="s">
+      <c r="E33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="E34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="E35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="4" t="s">
+      <c r="E36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="4" t="s">
+      <c r="E37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="4" t="s">
+      <c r="E38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="4" t="s">
+      <c r="E39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="4" t="s">
+      <c r="E40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="4" t="s">
+      <c r="E41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="4" t="s">
+      <c r="E42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="E43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" s="4" t="s">
+      <c r="E44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" s="4" t="s">
+      <c r="E45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="3" t="n">
         <v>2016</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="4" t="s">
+      <c r="E46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="3" t="n">
         <v>2017</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="4" t="s">
+      <c r="E47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="3" t="n">
         <v>2018</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="4" t="s">
+      <c r="E48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="3" t="n">
         <v>2019</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="4" t="s">
+      <c r="E49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F50" s="4" t="s">
+      <c r="E50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="4" t="s">
+      <c r="E51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="4" t="s">
+      <c r="E52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="4" t="s">
+      <c r="E53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="4" t="s">
+      <c r="E54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="4" t="s">
+      <c r="E55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2490,8 +2519,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="37.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="36.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="71.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="23.66"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2517,33 +2552,240 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="3" t="n">
         <f aca="false">COUNTIF(F5:F483,"Entregue")</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="3" t="n">
+        <v>2039</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="n">
+        <v>2033</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="3" t="n">
+        <v>2034</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="3" t="n">
+        <v>2041</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="n">
+        <v>2036</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="3" t="n">
+        <v>2043</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="3" t="n">
+        <v>2044</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2570,7 +2812,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2590,118 +2832,118 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>146</v>
+      <c r="G4" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="A5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>152</v>
+      <c r="F5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="A6" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>152</v>
+      <c r="F6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="A7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>152</v>
+      <c r="F7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="A8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>46295</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>152</v>
+      <c r="F8" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2726,12 +2968,13 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="44.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="28.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2753,162 +2996,162 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>165</v>
+      <c r="B4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <f aca="false">C5</f>
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <f aca="false">D5+C6</f>
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <f aca="false">D6+C7</f>
         <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <f aca="false">D7+C8</f>
         <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <f aca="false">D8+C9</f>
         <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="4" t="n">
+      <c r="A10" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <f aca="false">D9+C10</f>
         <v>49</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="4" t="n">
+      <c r="A11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <f aca="false">D10+C11</f>
         <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="4" t="n">
+      <c r="A12" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <f aca="false">D11+C12</f>
         <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="4" t="n">
+      <c r="A13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <f aca="false">D12+C13</f>
         <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="A14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <f aca="false">D13+C14</f>
         <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B15" s="4" t="n">
+      <c r="A15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <f aca="false">D14+C15</f>
         <v>49</v>
       </c>
@@ -2935,118 +3178,118 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="24.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>172</v>
+      <c r="A1" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>183</v>
+      <c r="A5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>183</v>
+      <c r="A6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>183</v>
+      <c r="A7" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3068,247 +3311,247 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="40.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="19.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="24.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>193</v>
+      <c r="A1" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>197</v>
+      <c r="G4" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>203</v>
+      <c r="B5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>203</v>
+      <c r="B6" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>203</v>
+      <c r="B7" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>203</v>
+      <c r="B8" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>203</v>
+      <c r="B10" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>203</v>
+      <c r="B11" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>203</v>
+      <c r="B12" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>203</v>
+      <c r="B13" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo da Sprint" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="257">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -613,43 +613,61 @@
     <t xml:space="preserve">Para que não ocorra atrasos no desenvolvimento, o acesso ao SnowFlake tem que esta disponivel no maximo ate 28.09.2026, uma vez que o desenvolvimento que se inicia em 05.10 depende estudo já pronto para a integração</t>
   </si>
   <si>
+    <t xml:space="preserve">Alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorizar liberações com a TR e manter ambiente local/mock enquanto pendente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente QA indisponível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem QA, a disponibilização da aplicação para homologação fica bloqueada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompanhar liberação do ambiente e validar checklist de deploy antecipadamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regras de negócios apresentando indefinições</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durante o levantamento dos requisitos do Sistema de Contratos, identificamos alguns pontos que ainda estão sendo discutidos e que possuem diferentes entendimentos sobre as regras de negócio por parte dos times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Médio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Média</t>
   </si>
   <si>
-    <t xml:space="preserve">Priorizar liberações com a TR e manter ambiente local/mock enquanto pendente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aberto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RI_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambiente QA indisponível</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem QA, a disponibilização da aplicação para homologação fica bloqueada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acompanhar liberação do ambiente e validar checklist de deploy antecipadamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RI_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mudança de escopo nas regras de negócio dos fluxos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alterações tardias nos fluxos Bizagi podem exigir retrabalho no código base já desenvolvido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Médio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congelar escopo por sprint e registrar mudanças via pendências/decisões.</t>
+    <t xml:space="preserve">Para conseguirmos avançar com mais segurança e evitar retrabalho durante o desenvolvimento, acreditamos que seria importante que esses pontos fossem alinhados e consolidados previamente entre os responsáveis pelo negócio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atraso na disponibilização do ambiente de QA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foi identificada como ponto de atenção a disponibilidade do servidor destinado ao ambiente de QA, necessário para a publicação, validação e homologação da aplicação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomenda-se priorizar a disponibilização e configuração do ambiente de QA e, paralelamente, manter o acompanhamento desse ponto junto às equipes envolvidas. Evitando assim, atraso na publicação da aplicação, e possível gargalo no processo de homologação.</t>
   </si>
   <si>
     <t xml:space="preserve">FLUXOS BIZAGI</t>
@@ -854,7 +872,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -869,6 +887,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3175,10 +3197,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="24.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="64.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="22.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3280,15 +3305,41 @@
         <v>206</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3319,32 +3370,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3352,22 +3403,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3375,22 +3426,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,22 +3449,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3421,22 +3472,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,22 +3495,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3467,22 +3518,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3490,22 +3541,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3513,22 +3564,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3536,22 +3587,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="288">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -460,24 +460,27 @@
     <t xml:space="preserve">Documento de requisitos Indexadores</t>
   </si>
   <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Indexadores, Ready Indexadores, Update Indexadores, Delete Indexadores) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste automatizado funcionalidade de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe</t>
+  </si>
+  <si>
     <t xml:space="preserve">A fazer</t>
   </si>
   <si>
-    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desenvolvimento da CRUD(Create Indexadores, Ready Indexadores, Update Indexadores, Delete Indexadores) referente a funcionalidade em questão.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teste automatizado funcionalidade de Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felipe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Documento de requisitos Segmentação</t>
   </si>
   <si>
@@ -502,6 +505,18 @@
     <t xml:space="preserve">Desenvolvimento da CRUD(Create Configurações Gerais, Ready Configurações Gerais, Update Configurações Gerais, Delete Configurações Gerais) referente a funcionalidade em questão.</t>
   </si>
   <si>
+    <t xml:space="preserve">Analise geral do acesso ao Snow Flake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta tarefa se resume em analisar os dados retornados pelo SnowFlake da Thomson Reuters, para implementação de da integraçao do o sistema de contratos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar VDI da TR para desenvolvimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar todas as ferramentas necessarias para desenvolvimento do projeto usando a VDI. 1-Git,2-Java Corretto 21,3-Eclipse,4-Vs code,5-NodesJS,6-Maven,7-Postgres,8-Plugis e dependencias que se fizerem necessárias</t>
+  </si>
+  <si>
     <t xml:space="preserve">PENDÊNCIAS, DÚVIDAS E DECISÕES</t>
   </si>
   <si>
@@ -523,36 +538,39 @@
     <t xml:space="preserve">Acesso TR – VDI</t>
   </si>
   <si>
-    <t xml:space="preserve">Liberação da VDI por parte da TR</t>
+    <t xml:space="preserve">Liberação da VDI(Edvaldo) por parte da TR</t>
   </si>
   <si>
     <t xml:space="preserve">Marcio </t>
   </si>
   <si>
+    <t xml:space="preserve">Resolvido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acesso- SnowFlake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberação de Acesso por parte da TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acesso – Power BI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Em análise</t>
   </si>
   <si>
-    <t xml:space="preserve">Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acesso- SnowFlake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liberação de Acesso por parte da TR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acesso – Power BI</t>
-  </si>
-  <si>
     <t xml:space="preserve">PD_04</t>
   </si>
   <si>
@@ -562,6 +580,39 @@
     <t xml:space="preserve">Liberação de Ambiente QA para disponibilizar a aplicação</t>
   </si>
   <si>
+    <t xml:space="preserve">PD_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acesso aos Excedentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criação de EndPoint para acesso às informações de Excedentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcestes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprovação dos Fluxos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprovação dos 5 primeiros Fluxos de Gestão de Contratos discutidos em reuniões de trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaqueline / Sérgio / Michael / Carlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluxo de Entitlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Após reunião com o time de Entitlement ficou decidido que o time TR - Entitlement iria definir  um fluxo de Complementação de Contrato, para apresentação.  Similar ao feito pela Bárbara / Dislaine.</t>
+  </si>
+  <si>
     <t xml:space="preserve">EVOLUÇÃO DAS ENTREGAS POR SPRINT</t>
   </si>
   <si>
@@ -607,25 +658,46 @@
     <t xml:space="preserve">RI_01</t>
   </si>
   <si>
-    <t xml:space="preserve">Dependência de acessos TR (VDI / Snowflake / Power BI)</t>
+    <t xml:space="preserve">Dependência de acessos TR – VDI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para que não ocorra atrasos no desenvolvimento, o acesso VDI de desenvolvimento precisa esta liberada o mais rapido possível.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorizar liberações com a TR e manter ambiente local de desenvolvimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependência de acessos TR  Snowflake</t>
   </si>
   <si>
     <t xml:space="preserve">Para que não ocorra atrasos no desenvolvimento, o acesso ao SnowFlake tem que esta disponivel no maximo ate 28.09.2026, uma vez que o desenvolvimento que se inicia em 05.10 depende estudo já pronto para a integração</t>
   </si>
   <si>
-    <t xml:space="preserve">Alta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Priorizar liberações com a TR e manter ambiente local/mock enquanto pendente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marcio</t>
+    <t xml:space="preserve">RI_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependência de acessos TR  Power BI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para que não ocorra atrasos no desenvolvimento, o acesso ao Power BI tem que esta disponivel no maximo ate 28.09.2026, uma vez que o desenvolvimento que se inicia em 05.10 depende estudo já pronto para a integração</t>
   </si>
   <si>
     <t xml:space="preserve">Aberto</t>
   </si>
   <si>
-    <t xml:space="preserve">RI_02</t>
+    <t xml:space="preserve">RI_04</t>
   </si>
   <si>
     <t xml:space="preserve">Ambiente QA indisponível</t>
@@ -637,7 +709,7 @@
     <t xml:space="preserve">Acompanhar liberação do ambiente e validar checklist de deploy antecipadamente.</t>
   </si>
   <si>
-    <t xml:space="preserve">RI_03</t>
+    <t xml:space="preserve">RI_05</t>
   </si>
   <si>
     <t xml:space="preserve">Regras de negócios apresentando indefinições</t>
@@ -658,7 +730,7 @@
     <t xml:space="preserve">Time TR</t>
   </si>
   <si>
-    <t xml:space="preserve">RI_04</t>
+    <t xml:space="preserve">RI_06</t>
   </si>
   <si>
     <t xml:space="preserve">Atraso na disponibilização do ambiente de QA </t>
@@ -685,13 +757,16 @@
     <t xml:space="preserve">AtualizadoEm</t>
   </si>
   <si>
+    <t xml:space="preserve">Passo a Passo</t>
+  </si>
+  <si>
     <t xml:space="preserve">oportunidade-em-andamento</t>
   </si>
   <si>
     <t xml:space="preserve">Oportunidade em Andamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Fluxo de oportunidade em andamento.</t>
+    <t xml:space="preserve">Fluxo iniciado por agendamento do sistema de contratos; processa oportunidades do Salesforce (Snowflake).</t>
   </si>
   <si>
     <t xml:space="preserve">oportunidade-em-andamento.png</t>
@@ -797,16 +872,35 @@
   </si>
   <si>
     <t xml:space="preserve">excedentes-mensal.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renovação Anual - Comunicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em andamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancelamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entitlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não iniciado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -829,16 +923,67 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -846,8 +991,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -871,9 +1023,37 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -881,27 +1061,196 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal 1" xfId="20"/>
+    <cellStyle name="Normal 5" xfId="21"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FF9C6500"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF006100"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF9C6500"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE2F0D9"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFF4CCCC"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF8000"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1084,275 +1433,283 @@
   </sheetPr>
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.33"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="5"/>
+      <c r="D5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="5"/>
+      <c r="G5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="5"/>
+      <c r="I5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="4"/>
+      <c r="D6" s="4" t="n">
         <f aca="false">SUM(B12:B15)</f>
         <v>41</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="G6" s="2" t="n">
+      <c r="E6" s="4"/>
+      <c r="G6" s="4" t="n">
         <f aca="false">SUM(C12:C15)</f>
         <v>41</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="n">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="n">
         <f aca="false">IFERROR(SUM(C12:C15)/SUM(B12:B15),0)</f>
         <v>1</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="e">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="e">
         <f aca="false">#ERR520!</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="3" t="e">
+      <c r="E9" s="1" t="e">
         <f aca="false">#ERR520!</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="str">
+      <c r="A12" s="1" t="str">
         <f aca="false">'Evolução do Projeto'!A5</f>
         <v>Sprint 0 - 13.07.2026 a 24.07.2026</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <f aca="false">'Evolução do Projeto'!B5</f>
         <v>3</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="1" t="n">
         <f aca="false">'Evolução do Projeto'!C5</f>
         <v>3</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="1" t="n">
         <f aca="false">IF(C12="", "", IFERROR(C12/B12,0))</f>
         <v>1</v>
       </c>
-      <c r="E12" s="3" t="str">
+      <c r="E12" s="1" t="str">
         <f aca="false">IF(C12="","Atualizar",IF(C12&gt;=B12,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F12" s="3" t="str">
+      <c r="F12" s="1" t="str">
         <f aca="false">IFERROR(MID(A12,FIND("-",A12)+2,99),"")</f>
         <v>13.07.2026 a 24.07.2026</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="str">
+      <c r="A13" s="1" t="str">
         <f aca="false">'Evolução do Projeto'!A6</f>
         <v>Sprint 1 - 27.07.2026 a 07.08.2026</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="1" t="n">
         <f aca="false">IF(C13="", "", IFERROR(C13/B13,0))</f>
         <v>1</v>
       </c>
-      <c r="E13" s="3" t="str">
+      <c r="E13" s="1" t="str">
         <f aca="false">IF(C13="","Atualizar",IF(C13&gt;=B13,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F13" s="3" t="str">
+      <c r="F13" s="1" t="str">
         <f aca="false">IFERROR(MID(A13,FIND("-",A13)+2,99),"")</f>
         <v>27.07.2026 a 07.08.2026</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="str">
+      <c r="A14" s="1" t="str">
         <f aca="false">'Evolução do Projeto'!A7</f>
         <v>Sprint 2 - 10.08.2026 a 21.08.2026</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="1" t="n">
         <f aca="false">IF(C14="", "", IFERROR(C14/B14,0))</f>
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="str">
+      <c r="E14" s="1" t="str">
         <f aca="false">IF(C14="","Atualizar",IF(C14&gt;=B14,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F14" s="3" t="str">
+      <c r="F14" s="1" t="str">
         <f aca="false">IFERROR(MID(A14,FIND("-",A14)+2,99),"")</f>
         <v>10.08.2026 a 21.08.2026</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="str">
+      <c r="A15" s="1" t="str">
         <f aca="false">'Evolução do Projeto'!A8</f>
         <v>Sprint 3 - 24.08.2026 a 04.09.2026</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="1" t="n">
         <f aca="false">'Evolução do Projeto'!B8</f>
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="1" t="n">
         <f aca="false">IF(C15="", "", IFERROR(C15/B15,0))</f>
         <v>1</v>
       </c>
-      <c r="E15" s="3" t="str">
+      <c r="E15" s="1" t="str">
         <f aca="false">IF(C15="","Atualizar",IF(C15&gt;=B15,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F15" s="3" t="str">
+      <c r="F15" s="1" t="str">
         <f aca="false">IFERROR(MID(A15,FIND("-",A15)+2,99),"")</f>
         <v>24.08.2026 a 04.09.2026</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="str">
+      <c r="A16" s="1" t="str">
         <f aca="false">'Evolução do Projeto'!A9</f>
         <v>Sprint 4 - 08.09.2026 a 18.09.2026</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="1" t="n">
         <f aca="false">'Evolução do Projeto'!B9</f>
         <v>10</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="1" t="n">
         <f aca="false">IF(C16="", "", IFERROR(C16/B16,0))</f>
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="str">
+      <c r="E16" s="1" t="str">
         <f aca="false">IF(C16="","Atualizar",IF(C16&gt;=B16,"Concluída","Parcial"))</f>
         <v>Concluída</v>
       </c>
-      <c r="F16" s="3" t="str">
+      <c r="F16" s="1" t="str">
         <f aca="false">IFERROR(MID(A16,FIND("-",A16)+2,99),"")</f>
         <v>08.09.2026 a 18.09.2026</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1387,1136 +1744,1137 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K55"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="40.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="42.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="37.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="10.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="I1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="I2" s="3" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="1" t="n">
         <f aca="false">COUNTA(B5:B500)</f>
         <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="1" t="n">
         <f aca="false">COUNTIF(F5:F500,"Entregue")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="8" t="n">
         <v>1947</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="8" t="n">
         <v>1948</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="F6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="8" t="n">
         <v>1949</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 1")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="8" t="n">
         <v>1961</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 2")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="8" t="n">
         <v>1962</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 3")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="8" t="n">
         <v>1963</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 4")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="8" t="n">
         <v>1967</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="E15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="8" t="n">
         <v>1969</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="E16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="E17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="E19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="E33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="E35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="E37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="E38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="E39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="E40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="E41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="3" t="s">
+      <c r="E42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="E43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="E45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="8" t="n">
         <v>2016</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="E46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="8" t="n">
         <v>2017</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="E47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="8" t="n">
         <v>2018</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="E48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="8" t="n">
         <v>2019</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="3" t="s">
+      <c r="E49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="E50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="8" t="n">
         <v>2021</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="E51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="E52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="E53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="3" t="s">
+      <c r="E54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="3" t="s">
+      <c r="E55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2541,275 +2899,357 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="37.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="36.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="71.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="23.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="63.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="1" t="n">
         <f aca="false">COUNTIF(F5:F483,"Entregue")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="1" t="n">
         <v>2030</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="n">
-        <v>2031</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="3" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>2032</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2039</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>2033</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>2034</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="n">
-        <v>2032</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="n">
-        <v>2039</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>2041</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="n">
-        <v>2033</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="F12" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>2036</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D13" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="n">
-        <v>2034</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D10" s="3" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>2043</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="n">
-        <v>2035</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="n">
-        <v>2041</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="E14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2044</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D16" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="n">
-        <v>2036</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="n">
-        <v>2043</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="n">
-        <v>2044</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="n">
-        <v>2045</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
+    </row>
+    <row r="17" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>2063</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H2"/>
@@ -2829,149 +3269,241 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.42"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>162</v>
+      <c r="G4" s="7" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="A5" s="14" t="s">
         <v>168</v>
       </c>
+      <c r="B5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="E8" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>168</v>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="F9:F11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>F9="Decidido"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>F9="Aberto"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>F9="Bloqueado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9:F11" type="list">
+      <formula1>"Aberto,Em análise,Decidido,Bloqueado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2989,191 +3521,187 @@
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="44.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="28.61"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>181</v>
+      <c r="B4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">C5</f>
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">D5+C6</f>
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">D6+C7</f>
         <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">D7+C8</f>
         <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="1" t="n">
         <f aca="false">D8+C9</f>
         <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="1" t="n">
         <f aca="false">D9+C10</f>
         <v>49</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="3" t="n">
+      <c r="A11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="1" t="n">
         <f aca="false">D10+C11</f>
         <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="3" t="n">
+      <c r="A12" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="1" t="n">
         <f aca="false">D11+C12</f>
         <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="3" t="n">
+      <c r="A13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="1" t="n">
         <f aca="false">D12+C13</f>
         <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="3" t="n">
+      <c r="A14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="1" t="n">
         <f aca="false">D13+C14</f>
         <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B15" s="3" t="n">
+      <c r="A15" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="1" t="n">
         <f aca="false">D14+C15</f>
         <v>49</v>
       </c>
@@ -3197,150 +3725,204 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="64.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="22.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="101.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="75.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>187</v>
+      <c r="A1" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="B4" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="10" t="s">
         <v>11</v>
       </c>
+      <c r="I4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>198</v>
+      <c r="A5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>198</v>
+      <c r="A6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>198</v>
+      <c r="A7" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>198</v>
+      <c r="F8" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3359,251 +3941,321 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="40.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="19.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="24.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="43.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>214</v>
+      <c r="A1" s="20" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>218</v>
+      <c r="G4" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>224</v>
+      <c r="B5" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>224</v>
+      <c r="B6" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>224</v>
+      <c r="B7" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>224</v>
+      <c r="B8" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>224</v>
+      <c r="B9" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>224</v>
+      <c r="B10" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="B11" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>224</v>
+      <c r="G11" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>224</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>224</v>
-      </c>
+      <c r="B13" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -838,6 +838,24 @@
     <t xml:space="preserve">validacao-oportunidades-renovacao.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Em andamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renovação Anual - Comunicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancelamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entitlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nao iniciado</t>
+  </si>
+  <si>
     <t xml:space="preserve">recupera-dados-de-consumo</t>
   </si>
   <si>
@@ -872,24 +890,6 @@
   </si>
   <si>
     <t xml:space="preserve">excedentes-mensal.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renovação Anual - Comunicação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em andamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancelamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entitlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não iniciado</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1144,7 @@
     <cellStyle name="Normal 1" xfId="20"/>
     <cellStyle name="Normal 5" xfId="21"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1187,6 +1187,21 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3947,9 +3962,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="43.42"/>
   </cols>
@@ -4118,140 +4133,140 @@
       <c r="E10" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>248</v>
+      <c r="F10" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="14" t="s">
+      <c r="G11" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="E11" s="14" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G11" s="14" t="s">
+      <c r="C12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G12" s="14" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G13" s="14" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo da Sprint" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="290">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -463,9 +463,6 @@
     <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Indexadores</t>
   </si>
   <si>
-    <t xml:space="preserve">Fazendo</t>
-  </si>
-  <si>
     <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Indexadores</t>
   </si>
   <si>
@@ -478,24 +475,24 @@
     <t xml:space="preserve">Felipe</t>
   </si>
   <si>
+    <t xml:space="preserve">Documento de requisitos Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Segmentação, Ready Segmentação, Update Segmentação, Delete Segmentação) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste automatizado funcionalidade de Segmentação</t>
+  </si>
+  <si>
     <t xml:space="preserve">A fazer</t>
   </si>
   <si>
-    <t xml:space="preserve">Documento de requisitos Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desenvolvimento da CRUD(Create Segmentação, Ready Segmentação, Update Segmentação, Delete Segmentação) referente a funcionalidade em questão.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teste automatizado funcionalidade de Segmentação</t>
-  </si>
-  <si>
     <t xml:space="preserve">BackEnd referente a funcionalidade Configurações Gerais</t>
   </si>
   <si>
@@ -890,6 +887,15 @@
   </si>
   <si>
     <t xml:space="preserve">excedentes-mensal.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retorno do comunicado do e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluxo do retorno do comunicado do e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1150,7 @@
     <cellStyle name="Normal 1" xfId="20"/>
     <cellStyle name="Normal 5" xfId="21"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1187,21 +1193,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3013,7 +3004,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3024,16 +3015,16 @@
         <v>2032</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="E7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3047,13 +3038,13 @@
         <v>135</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3067,13 +3058,13 @@
         <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3084,7 +3075,7 @@
         <v>2034</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>45</v>
@@ -3093,7 +3084,7 @@
         <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3104,16 +3095,16 @@
         <v>2035</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3127,13 +3118,13 @@
         <v>135</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3147,13 +3138,13 @@
         <v>68</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3164,7 +3155,7 @@
         <v>2043</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>45</v>
@@ -3173,7 +3164,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3184,16 +3175,16 @@
         <v>2044</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E15" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3207,13 +3198,13 @@
         <v>135</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3224,16 +3215,16 @@
         <v>2063</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>160</v>
-      </c>
       <c r="E17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3244,16 +3235,16 @@
         <v>2165</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3297,7 +3288,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3321,181 +3312,181 @@
         <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>171</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F5" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>172</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
         <v>176</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>177</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>172</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>179</v>
-      </c>
       <c r="C7" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>176</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>177</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>183</v>
-      </c>
       <c r="D8" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="17" t="s">
         <v>186</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>187</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>46326</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="D10" s="17" t="s">
         <v>190</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>191</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>194</v>
-      </c>
       <c r="D11" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3539,7 +3530,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3565,13 +3556,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3663,7 +3654,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>8</v>
@@ -3675,7 +3666,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>16</v>
@@ -3687,7 +3678,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>6</v>
@@ -3699,7 +3690,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -3711,7 +3702,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>4</v>
@@ -3752,7 +3743,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3762,19 +3753,19 @@
         <v>21</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>24</v>
@@ -3786,158 +3777,158 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3962,7 +3953,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.87"/>
@@ -3971,35 +3962,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>240</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>241</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4007,22 +3998,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4030,22 +4021,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="F6" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4053,22 +4044,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="F7" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4076,22 +4067,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="E8" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>261</v>
-      </c>
       <c r="F8" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4099,22 +4090,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="E9" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>265</v>
-      </c>
       <c r="F9" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4122,22 +4113,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="E10" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="F10" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="G10" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4145,19 +4136,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>271</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4165,19 +4156,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4185,19 +4176,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="G13" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4205,22 +4196,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="E14" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>279</v>
-      </c>
       <c r="F14" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4228,22 +4219,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="E15" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>283</v>
-      </c>
       <c r="F15" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,26 +4242,43 @@
         <v>12</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="E16" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="F16" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
+      <c r="C17" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>289</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="291">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -565,30 +565,33 @@
     <t xml:space="preserve">Acesso – Power BI</t>
   </si>
   <si>
+    <t xml:space="preserve">Em atraso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiente QA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberação de Ambiente QA para disponibilizar a aplicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acesso aos Excedentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criação de EndPoint para acesso às informações de Excedentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcestes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Em análise</t>
   </si>
   <si>
-    <t xml:space="preserve">PD_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambiente QA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liberação de Ambiente QA para disponibilizar a aplicação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acesso aos Excedentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criação de EndPoint para acesso às informações de Excedentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alcestes</t>
-  </si>
-  <si>
     <t xml:space="preserve">PD_06</t>
   </si>
   <si>
@@ -835,16 +838,16 @@
     <t xml:space="preserve">validacao-oportunidades-renovacao.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Renovação Anual - Comunicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancelamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Em andamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renovação Anual - Comunicação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancelamento</t>
   </si>
   <si>
     <t xml:space="preserve">Entitlement</t>
@@ -3439,7 +3442,7 @@
         <v>46326</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>172</v>
@@ -3447,21 +3450,21 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>46290</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="14" t="s">
         <v>179</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -3470,20 +3473,20 @@
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="18" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>172</v>
@@ -3493,7 +3496,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F9:F11">
+  <conditionalFormatting sqref="F11 F9">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>F9="Decidido"</formula>
     </cfRule>
@@ -3505,7 +3508,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9:F11" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9 F11" type="list">
       <formula1>"Aberto,Em análise,Decidido,Bloqueado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3530,7 +3533,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3556,13 +3559,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3654,7 +3657,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>8</v>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>16</v>
@@ -3678,7 +3681,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>6</v>
@@ -3690,7 +3693,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -3702,7 +3705,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>4</v>
@@ -3743,7 +3746,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3753,19 +3756,19 @@
         <v>21</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>166</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>24</v>
@@ -3777,25 +3780,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>171</v>
@@ -3803,25 +3806,25 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>171</v>
@@ -3829,106 +3832,106 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3962,35 +3965,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3998,22 +4001,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4021,22 +4024,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>249</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,22 +4047,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4067,22 +4070,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4090,22 +4093,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4113,22 +4116,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="F10" s="1" t="s">
         <v>269</v>
       </c>
+      <c r="F10" s="14" t="s">
+        <v>248</v>
+      </c>
       <c r="G10" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4145,7 +4148,7 @@
         <v>270</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>271</v>
@@ -4165,7 +4168,7 @@
         <v>272</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>271</v>
@@ -4176,16 +4179,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>271</v>
@@ -4196,22 +4199,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4219,22 +4222,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4242,22 +4245,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4265,19 +4268,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo da Sprint" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="292">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -490,9 +490,6 @@
     <t xml:space="preserve">Teste automatizado funcionalidade de Segmentação</t>
   </si>
   <si>
-    <t xml:space="preserve">A fazer</t>
-  </si>
-  <si>
     <t xml:space="preserve">BackEnd referente a funcionalidade Configurações Gerais</t>
   </si>
   <si>
@@ -502,6 +499,9 @@
     <t xml:space="preserve">Desenvolvimento da CRUD(Create Configurações Gerais, Ready Configurações Gerais, Update Configurações Gerais, Delete Configurações Gerais) referente a funcionalidade em questão.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fazendo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Analise geral do acesso ao Snow Flake</t>
   </si>
   <si>
@@ -772,58 +772,61 @@
     <t xml:space="preserve">oportunidade-em-andamento.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Aprovado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluxo New Name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-name.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-base-cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Base (Cliente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluxo de nova base de cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-base-cliente.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-base-produto-ou-modulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Base (Produto ou Módulo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluxo de nova base de produto ou módulo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-base-produto-ou-modulo.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complementacao-do-contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complementação do Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluxo de complementação de dados do contrato.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complementacao-do-contrato.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aguardando aprovação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new-name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluxo New Name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new-name.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new-base-cliente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Base (Cliente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluxo de nova base de cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new-base-cliente.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new-base-produto-ou-modulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Base (Produto ou Módulo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluxo de nova base de produto ou módulo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new-base-produto-ou-modulo.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">complementacao-do-contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complementação do Contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluxo de complementação de dados do contrato.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">complementacao-do-contrato.png</t>
   </si>
   <si>
     <t xml:space="preserve">validacao-oportunidades-renovacao</t>
@@ -3147,7 +3150,7 @@
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3158,7 +3161,7 @@
         <v>2043</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>45</v>
@@ -3167,7 +3170,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3178,16 +3181,16 @@
         <v>2044</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E15" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3207,7 +3210,7 @@
         <v>148</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3465,7 +3468,7 @@
         <v>46290</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>172</v>
@@ -3530,6 +3533,9 @@
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.44"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
@@ -3650,9 +3656,12 @@
       <c r="B10" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="C10" s="0" t="n">
+        <v>9</v>
+      </c>
       <c r="D10" s="1" t="n">
         <f aca="false">D9+C10</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3664,7 +3673,7 @@
       </c>
       <c r="D11" s="1" t="n">
         <f aca="false">D10+C11</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3676,7 +3685,7 @@
       </c>
       <c r="D12" s="1" t="n">
         <f aca="false">D11+C12</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3688,7 +3697,7 @@
       </c>
       <c r="D13" s="1" t="n">
         <f aca="false">D12+C13</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3700,7 +3709,7 @@
       </c>
       <c r="D14" s="1" t="n">
         <f aca="false">D13+C14</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3712,7 +3721,7 @@
       </c>
       <c r="D15" s="1" t="n">
         <f aca="false">D14+C15</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4105,7 +4114,7 @@
         <v>265</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>249</v>
@@ -4116,19 +4125,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>266</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>248</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>249</v>
@@ -4139,19 +4148,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4159,19 +4168,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>272</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4179,19 +4188,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,19 +4208,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>249</v>
@@ -4222,19 +4231,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>249</v>
@@ -4245,19 +4254,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>249</v>
@@ -4268,19 +4277,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/conteudo/Sprint_Review_Controle_Entregas.xlsx
+++ b/conteudo/Sprint_Review_Controle_Entregas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo da Sprint" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="290">
   <si>
     <t xml:space="preserve">RESUMO GERAL DAS SPRINTS — SISTEMA DE GESTÃO DE CONTRATOS</t>
   </si>
@@ -70,9 +70,6 @@
     <t xml:space="preserve">OBSERVAÇÃO DE CONTROLE</t>
   </si>
   <si>
-    <t xml:space="preserve">A aprovação dos Fluxos() deverão ocorrer na próxima sprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">HISTÓRICO DE FUNCIONALIDADES ENTREGUES</t>
   </si>
   <si>
@@ -451,67 +448,67 @@
     <t xml:space="preserve">Desenvolvimento da CRUD(Create ERPS, Ready ERPS, Update ERPS, Delete ERPS) referente a funcionalidade em questão.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprint 5 - 21.09.2026 a 02.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento de requisitos Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Indexadores, Ready Indexadores, Update Indexadores, Delete Indexadores) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste automatizado funcionalidade de Indexadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento de requisitos Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Segmentação, Ready Segmentação, Update Segmentação, Delete Segmentação) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste automatizado funcionalidade de Segmentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackEnd referente a funcionalidade Configurações Gerais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd referente a funcionalidade Configurações Gerais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenvolvimento da CRUD(Create Configurações Gerais, Ready Configurações Gerais, Update Configurações Gerais, Delete Configurações Gerais) referente a funcionalidade em questão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analise geral do acesso ao Snow Flake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta tarefa se resume em analisar os dados retornados pelo SnowFlake da Thomson Reuters, para implementação de da integraçao do o sistema de contratos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar VDI da TR para desenvolvimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar todas as ferramentas necessarias para desenvolvimento do projeto usando a VDI. 1-Git,2-Java Corretto 21,3-Eclipse,4-Vs code,5-NodesJS,6-Maven,7-Postgres,8-Plugis e dependencias que se fizerem necessárias</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLANEJAMENTO DA PRÓXIMA SPRINT</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint 5 - 21.09.2026 a 02.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documento de requisitos Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desenvolvimento da CRUD(Create Indexadores, Ready Indexadores, Update Indexadores, Delete Indexadores) referente a funcionalidade em questão.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teste automatizado funcionalidade de Indexadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documento de requisitos Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackEnd referente a funcionalidade manutenção de Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FrontEnd referente a funcionalidade manutenção de Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desenvolvimento da CRUD(Create Segmentação, Ready Segmentação, Update Segmentação, Delete Segmentação) referente a funcionalidade em questão.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teste automatizado funcionalidade de Segmentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackEnd referente a funcionalidade Configurações Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FrontEnd referente a funcionalidade Configurações Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desenvolvimento da CRUD(Create Configurações Gerais, Ready Configurações Gerais, Update Configurações Gerais, Delete Configurações Gerais) referente a funcionalidade em questão.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fazendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analise geral do acesso ao Snow Flake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esta tarefa se resume em analisar os dados retornados pelo SnowFlake da Thomson Reuters, para implementação de da integraçao do o sistema de contratos. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparar VDI da TR para desenvolvimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalar todas as ferramentas necessarias para desenvolvimento do projeto usando a VDI. 1-Git,2-Java Corretto 21,3-Eclipse,4-Vs code,5-NodesJS,6-Maven,7-Postgres,8-Plugis e dependencias que se fizerem necessárias</t>
+    <t xml:space="preserve">Sprint 6 - 05.10.2026 a 16.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">PENDÊNCIAS, DÚVIDAS E DECISÕES</t>
@@ -623,9 +620,6 @@
   </si>
   <si>
     <t xml:space="preserve">Entregas acumuladas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 6 - 05.10.2026 a 16.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint 7 - 19.10.2026 a 30.10.2026</t>
@@ -918,7 +912,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -937,15 +930,15 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -953,14 +946,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1160,7 +1152,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="2"/>
         <b val="1"/>
         <color rgb="FF006100"/>
@@ -1175,7 +1166,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="2"/>
         <b val="1"/>
         <color rgb="FF9C6500"/>
@@ -1190,7 +1180,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="2"/>
         <b val="1"/>
         <color rgb="FFC00000"/>
@@ -1309,14 +1298,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1324,55 +1313,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1390,48 +1349,12 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -1443,7 +1366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.78"/>
@@ -1714,15 +1637,36 @@
         <v>08.09.2026 a 18.09.2026</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="str">
+        <f aca="false">'Evolução do Projeto'!A10</f>
+        <v>Sprint 5 - 21.09.2026 a 02.10.2026</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <f aca="false">'Evolução do Projeto'!B10</f>
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <f aca="false">IF(C17="", "", IFERROR(C17/B17,0))</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f aca="false">IF(C17="","Atualizar",IF(C17&gt;=B17,"Concluída","Parcial"))</f>
+        <v>Concluída</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <f aca="false">IFERROR(MID(A17,FIND("-",A17)+2,99),"")</f>
+        <v>21.09.2026 a 02.10.2026</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1755,7 +1699,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.17"/>
@@ -1766,7 +1710,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1775,14 +1719,14 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
       <c r="I1" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1791,19 +1735,19 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="n">
         <f aca="false">COUNTA(B5:B500)</f>
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1811,25 +1755,25 @@
         <v>7</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>24</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">COUNTIF(F5:F500,"Entregue")</f>
@@ -1838,71 +1782,71 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>1947</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>1948</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>1949</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="K7" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 1")</f>
@@ -1911,25 +1855,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>1961</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="K8" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 2")</f>
@@ -1938,25 +1882,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>1962</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="K9" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 3")</f>
@@ -1965,25 +1909,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>1963</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="K10" s="1" t="n">
         <f aca="false">COUNTIF(A5:A500,"Sprint 4")</f>
@@ -1992,902 +1936,1182 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>1973</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>1974</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>1975</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>1967</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>1968</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>1969</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="C34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B37" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B39" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B40" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B42" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B45" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B46" s="8" t="n">
         <v>2016</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B47" s="8" t="n">
         <v>2017</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B48" s="8" t="n">
         <v>2018</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B49" s="8" t="n">
         <v>2019</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B50" s="8" t="n">
         <v>2020</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B51" s="8" t="n">
         <v>2021</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B52" s="8" t="n">
         <v>2022</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B53" s="8" t="n">
         <v>2024</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B54" s="8" t="n">
         <v>2025</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B55" s="8" t="n">
         <v>2026</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>31</v>
+      <c r="B56" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>2032</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>2039</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>2033</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>2034</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>2041</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>2036</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>2043</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>2044</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>2063</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2921,7 +3145,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2947,26 +3171,26 @@
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">COUNTIF(F5:F483,"Entregue")</f>
@@ -2975,283 +3199,107 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>143</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>2031</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>2032</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="B7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1"/>
+      <c r="E8" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>2039</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>2033</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>2034</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>2035</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>152</v>
-      </c>
+      <c r="B11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>2041</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="B12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>2036</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>2043</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>2044</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="B15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>2045</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="B16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>2063</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>159</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
       <c r="E17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>2165</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>161</v>
-      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="12"/>
       <c r="E18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3294,7 +3342,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3315,184 +3363,184 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>169</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>170</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F5" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="C7" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>182</v>
-      </c>
       <c r="D8" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="17" t="s">
         <v>185</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>186</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>46326</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="D10" s="17" t="s">
         <v>190</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>191</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>46290</v>
       </c>
       <c r="F10" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>194</v>
-      </c>
       <c r="D11" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3511,7 +3559,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9 F11" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9 F11" type="list">
       <formula1>"Aberto,Em análise,Decidido,Bloqueado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3534,12 +3582,12 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3565,18 +3613,18 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>3</v>
@@ -3591,7 +3639,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>10</v>
@@ -3606,7 +3654,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>14</v>
@@ -3621,7 +3669,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>12</v>
@@ -3636,7 +3684,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>10</v>
@@ -3651,77 +3699,77 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>9</v>
+      <c r="C10" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="n">
         <f aca="false">D9+C10</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="n">
         <f aca="false">D10+C11</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
         <f aca="false">D11+C12</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
         <f aca="false">D12+C13</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="n">
         <f aca="false">D13+C14</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="1" t="n">
         <f aca="false">D14+C15</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3755,32 +3803,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>11</v>
@@ -3789,158 +3837,158 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -3974,35 +4022,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>239</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>241</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4010,22 +4058,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>247</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4033,22 +4081,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="F6" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4056,22 +4104,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="E7" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="F7" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4079,22 +4127,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>261</v>
-      </c>
       <c r="F8" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4102,22 +4150,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>266</v>
-      </c>
       <c r="G9" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4125,22 +4173,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="E10" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>270</v>
-      </c>
       <c r="F10" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4148,19 +4196,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4168,19 +4216,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4188,19 +4236,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4208,22 +4256,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="E14" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>280</v>
-      </c>
       <c r="F14" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4231,22 +4279,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="E15" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>284</v>
-      </c>
       <c r="F15" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4254,22 +4302,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="E16" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>288</v>
-      </c>
       <c r="F16" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4277,19 +4325,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>289</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>
